--- a/doc/docs/股票配置.xlsx
+++ b/doc/docs/股票配置.xlsx
@@ -1,19 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\proj\unityProj\Line\doc\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8FA5B05-BDFC-419E-BB95-837874CFEDED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E66D6846-FD9A-48DA-826B-1CC1F5DA8F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="504" windowWidth="30984" windowHeight="16560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="StockCfg" sheetId="3" r:id="rId1"/>
+    <sheet name="股票属性" sheetId="6" r:id="rId1"/>
+    <sheet name="股票属性枚举" sheetId="7" r:id="rId2"/>
+    <sheet name="决策链" sheetId="3" r:id="rId3"/>
+    <sheet name="决策链类型" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="199">
   <si>
     <t>Horizontal</t>
   </si>
@@ -40,51 +43,281 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>股票id</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stock</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>stockName#string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>股票名</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>baseVolatility#float</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>基础波动性</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>originPrice#float</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>初始价格</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>石油</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>钢铁</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>棉花</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>symbol#string</t>
+    <t>决策链id</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>serialId#int</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>round#int</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>name#string</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>attrs#string[]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>决策链系列</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>决策链名称</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合数</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>平稳发展</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性（attr#回合数*延迟)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["2"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["2","8#2*2"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["5"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["5","8#2*2"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>冒险与突破</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["20#3","3*2","10#1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["20#1","21#1*1","3*1","19*2"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["20#2","14#1","3"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["20#3","14#2","13#2*2","2#4","3*4"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>desc#string</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>决策链描述</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>StockStrategy</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>StockStrategySerial</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>业绩稳定驱动，公司稳定发展，正常波动，无不良迹象</t>
+  </si>
+  <si>
+    <t>公司做了一些冒险的尝试，取得了突破性的成果</t>
+  </si>
+  <si>
+    <t>冒险与挫折</t>
+  </si>
+  <si>
+    <t>公司做了一些冒险的尝试 ，但结局并不理想</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>疲软无力</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>重振旗鼓</t>
+  </si>
+  <si>
+    <t>马拉松</t>
+  </si>
+  <si>
+    <t>违规操作</t>
+  </si>
+  <si>
+    <t>野蛮生长</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>精简优化</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["20#3","21*2","6#1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["20#1","21#1*1","6#1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["20#2","14#1","6"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["20#3","10#2","13#2*2","5#4","6*4"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>emotion#int</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>影响类型（0中立，1积极，2消极）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["5","9#2","21*1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["9","8*1","13#1*1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["15","21"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["5","21"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["19#2","8","5#1","2#1*1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["14","2"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["18","19","13*1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["19","2"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["5#2","18#2*1","16@2"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["5#4","16*2","9*4"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["2","17#6","9*4"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["5","18#4","16*2"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["2#4","16*2","12*4"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["20#4","21*4","8","19#2*3"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["6#1","4#2*1","12*1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["20#2","4#2*1","7*3","21*3"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["13","16#2","9#2*1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["4#1","10","11*1","7*2"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["17","16*1","5#2"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["16","13*2"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["17","9#2","14*2"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["5","18","21"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["5#1","2*1","19","10"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["19","8*1","13#2"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["18","14*1","3#2"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>StockAttr</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>key#string</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect1#string[]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect2#string[]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect3#string[]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>词条id</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>名称</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -92,23 +325,483 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>oil</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>steel</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>cotton</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>描述</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始时效果</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>股价计算前效果</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合清算时效果</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>未知</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>unknown</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>公司发展有一些变化，但还不清楚有什么影响</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>[]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>爬升</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>up_slow</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日公司业绩额外上升0.1，若业绩上升，再放大10%</t>
+  </si>
+  <si>
+    <t>["Add#0.1","UpScale#1.1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>高歌</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>up_middle</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日公司业绩额外上升0.3，若业绩上升，再放大20%</t>
+  </si>
+  <si>
+    <t>["Add#0.3","UpScale1.2"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>火箭</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>up_fast</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日公司业绩额外上升0.5，若业绩上升，再放大30%</t>
+  </si>
+  <si>
+    <t>["Add#0.5","UpScale#1.3"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑坡</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>fall_slow</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日公司业绩额外下降0.1，若业绩下降，再放大10%</t>
+  </si>
+  <si>
+    <t>["Add#-0.1","DownScale#1.1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>摔落</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>fall_middle</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日公司业绩额外下降0.3，若业绩下降，再放大20%</t>
+  </si>
+  <si>
+    <t>["Add#-0.3","DownScale#1.1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>断崖</t>
+  </si>
+  <si>
+    <t>fall_fast</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日公司业绩额外下降0.5，若业绩下降，再放大30%</t>
+  </si>
+  <si>
+    <t>["Add#-0.5","DownScale#1.3"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>摇摆</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>pingpong</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日，若上个交易日公司业绩上升，则此次业绩缩减15%，若上个交易日公司业绩下降，则此次业绩放大15%</t>
+  </si>
+  <si>
+    <t>["UpScaleLast#0.85","DownScaleLast#1.15"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>懒散</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>lazy</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日，公司业绩变化缩减30%</t>
+  </si>
+  <si>
+    <t>["Scale#0.3"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>敏感</t>
+  </si>
+  <si>
+    <t>sensitive</t>
+  </si>
+  <si>
+    <t>每日8%的公司实力变为市场敏感度</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Transfer#1#2#0.08"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>盲从</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>blindly</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日8%的公司实力变为行业冲击乘数</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Transfer#1#3#0.08"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>腐败</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>corruption</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日5%的公司实力变为市场敏感度，5%的公司实力变为行业冲击乘数，交易日结束后各增加5%并给予【滑坡*】</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Transfer#1#2#0.05*1","Transfer#1#3#0.05*1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["GrowAdd#1#0.05","AttrAdd#5#-1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>混乱</t>
+  </si>
+  <si>
+    <t>chaotic</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日，1/3概率业绩上升0.4，1/3概率业绩放大30%，1/3概率业绩下降0.6</t>
+  </si>
+  <si>
+    <t>["Add#0.4%1","Scale#1.3%1","Add#-0.6%1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>创新</t>
+  </si>
+  <si>
+    <t>innovative</t>
+  </si>
+  <si>
+    <t>每回合8%行业冲击乘数变为公司实力</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Transfer#3#1#0.08"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>衰老</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>aging</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日公司业绩额外下降0.15，交易日结束时该值增加0.2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Add#-0.15*1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["GrowAdd#1#0.2"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>生长</t>
+  </si>
+  <si>
+    <t>growing</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日业绩额外上升0.2，交易日结束时该值增加0.1，3/1概率8%行业冲击乘数变为公司实力</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Transfer#3#1#0.08%0.33"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Add#0.2*1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["GrowAdd#1#0.1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>扩张</t>
+  </si>
+  <si>
+    <t>expanding</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日业绩扩大35%，交易日结束时该值减少7%，20%公司实力变为市场敏感度，交易日结束时该值减少8%</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Transfer#1#2#0.2*1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Scale#1.35*2"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["GrowAdd#1#-0.08","GrowAdd#2#-0.07"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>精简</t>
+  </si>
+  <si>
+    <t>streamline</t>
+  </si>
+  <si>
+    <t>每日业绩缩减20%，交易日结束时该值减少5%，10%行业冲击乘数变为公司实力，交易日结束时该值增加8%</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Transfer#3#1#0.1*1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Scale#0.8*2"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["GrowAdd#1#0.08","GrowAdd#2#0.05"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>整顿</t>
+  </si>
+  <si>
+    <t>rectify</t>
+  </si>
+  <si>
+    <t>每日5%市场敏感度和5%行业冲击乘数变为公司实力，交易日结束后各增加3%，1/3概率移除一条负面属性*</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Transfer#2#1#0.05*1","Transfer#3#1#0.05*1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["GrowAdd#1#0.03","AttrPurify#1%0.3"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>冒险</t>
+  </si>
+  <si>
+    <t>adventure</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日8%行业冲击乘数变为市场敏感度</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Transfer#3#2#0.08"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>停滞</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>stagnant</t>
+  </si>
+  <si>
+    <t>每回合8%市场敏感度变为行业冲击乘数</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Transfer#2#3#0.08"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enum</t>
+  </si>
+  <si>
+    <t>1|2</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>值</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Up_Slow</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Up_Middle</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Up_Fast</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fall_Slow</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fall_Middle</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fall_Fast</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pingpong</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lazy</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sensitive</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blindly</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Corruption</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chaotic</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Innovative</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aging</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Growing</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Expanding</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Streamline</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rectify</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adventure</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stagant</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>StockAttrType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum#StockAttrType</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,6 +848,12 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -170,7 +869,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -187,6 +886,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom style="double">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -196,7 +906,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -204,9 +914,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1">
@@ -222,6 +929,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -491,27 +1204,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C30EA875-D284-4283-9E71-3B7873A46ECE}">
+  <dimension ref="A1:L28"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.59765625" customWidth="1"/>
-    <col min="2" max="2" width="16.59765625" customWidth="1"/>
-    <col min="3" max="3" width="21.06640625" customWidth="1"/>
-    <col min="4" max="4" width="19.59765625" customWidth="1"/>
-    <col min="5" max="5" width="24.3984375" customWidth="1"/>
-    <col min="6" max="6" width="18.19921875" customWidth="1"/>
-    <col min="7" max="7" width="20.46484375" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" customWidth="1"/>
+    <col min="4" max="4" width="41.77734375" customWidth="1"/>
+    <col min="5" max="5" width="52.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="48.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="48.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.33203125" customWidth="1"/>
-    <col min="9" max="9" width="23.19921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.46484375" customWidth="1"/>
+    <col min="9" max="9" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.44140625" customWidth="1"/>
     <col min="11" max="11" width="14.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.46484375" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -520,55 +1233,61 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
+    <row r="3" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>198</v>
+      </c>
       <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="6"/>
-      <c r="G3" s="7"/>
-    </row>
-    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="E3" s="1"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="6"/>
+    </row>
+    <row r="4" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" s="1">
@@ -577,109 +1296,1744 @@
       <c r="E5" s="1">
         <v>1</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
       <c r="H5" s="1"/>
-      <c r="I5" s="4"/>
+      <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
-    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:12" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:12" ht="16.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>7</v>
+        <v>72</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+        <v>75</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
     </row>
-    <row r="8" spans="1:12" ht="13.9" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="3">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>100</v>
-      </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="B8" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+    </row>
+    <row r="9" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>100</v>
-      </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="B9" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>3</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+    </row>
+    <row r="11" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>4</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>5</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>6</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>8</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>9</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>10</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>11</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>12</v>
       </c>
+      <c r="B19" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>13</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>14</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C21" t="s">
+        <v>132</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>15</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>16</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>17</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>18</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C25" t="s">
+        <v>153</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>19</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C26" t="s">
+        <v>159</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>20</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>21</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C28" t="s">
+        <v>168</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{372E5726-183E-4D18-BDE8-1D38ACB940CB}">
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="16.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B7" s="1">
+        <v>5</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="1">
+        <v>6</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B9" s="1">
+        <v>7</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B10" s="1">
+        <v>8</v>
+      </c>
       <c r="C10" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B11" s="1">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B12" s="1">
+        <v>10</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B13" s="1">
+        <v>11</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B14" s="1">
+        <v>12</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B15" s="1">
+        <v>13</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B16" s="1">
+        <v>14</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B17" s="1">
+        <v>15</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B18" s="1">
+        <v>16</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B19" s="1">
         <v>17</v>
       </c>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1">
-        <v>100</v>
-      </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="3"/>
+      <c r="C19" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B20" s="1">
+        <v>18</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B21" s="1">
+        <v>19</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="B22" s="1">
+        <v>20</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B23" s="1">
+        <v>21</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:L118"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.44140625" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="20.44140625" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" customWidth="1"/>
+    <col min="9" max="9" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.44140625" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="5"/>
+      <c r="H3" s="6"/>
+    </row>
+    <row r="4" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:12" ht="16.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+    </row>
+    <row r="8" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+    </row>
+    <row r="9" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>2</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+    </row>
+    <row r="10" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>5</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1">
+        <v>3</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1">
+        <v>5</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>7</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>8</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1">
+        <v>4</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>9</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1">
+        <v>3</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>10</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>11</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18" s="1">
+        <v>5</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>12</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19" s="1">
+        <v>4</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>13</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20" s="1">
+        <v>3</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>14</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>15</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+      <c r="C22" s="1">
+        <v>5</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>16</v>
+      </c>
+      <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23" s="1">
+        <v>3</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>17</v>
+      </c>
+      <c r="B24">
+        <v>4</v>
+      </c>
+      <c r="C24" s="1">
+        <v>3</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>18</v>
+      </c>
+      <c r="B25">
+        <v>4</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>19</v>
+      </c>
+      <c r="B26">
+        <v>4</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>20</v>
+      </c>
+      <c r="B27">
+        <v>5</v>
+      </c>
+      <c r="C27" s="1">
+        <v>3</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>21</v>
+      </c>
+      <c r="B28">
+        <v>5</v>
+      </c>
+      <c r="C28" s="1">
+        <v>3</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>22</v>
+      </c>
+      <c r="B29">
+        <v>5</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>23</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30" s="1">
+        <v>1</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>24</v>
+      </c>
+      <c r="B31">
+        <v>5</v>
+      </c>
+      <c r="C31" s="1">
+        <v>5</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>25</v>
+      </c>
+      <c r="B32">
+        <v>6</v>
+      </c>
+      <c r="C32" s="1">
+        <v>7</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>26</v>
+      </c>
+      <c r="B33">
+        <v>6</v>
+      </c>
+      <c r="C33" s="1">
+        <v>8</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>27</v>
+      </c>
+      <c r="B34">
+        <v>6</v>
+      </c>
+      <c r="C34" s="1">
+        <v>6</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>28</v>
+      </c>
+      <c r="B35">
+        <v>6</v>
+      </c>
+      <c r="C35" s="1">
+        <v>7</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>29</v>
+      </c>
+      <c r="B36">
+        <v>6</v>
+      </c>
+      <c r="C36" s="1">
+        <v>8</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>30</v>
+      </c>
+      <c r="B37">
+        <v>7</v>
+      </c>
+      <c r="C37" s="1">
+        <v>5</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>31</v>
+      </c>
+      <c r="B38">
+        <v>7</v>
+      </c>
+      <c r="C38" s="1">
+        <v>5</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>32</v>
+      </c>
+      <c r="B39">
+        <v>7</v>
+      </c>
+      <c r="C39">
+        <v>4</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>33</v>
+      </c>
+      <c r="B40">
+        <v>7</v>
+      </c>
+      <c r="C40" s="1">
+        <v>3</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>34</v>
+      </c>
+      <c r="B41">
+        <v>8</v>
+      </c>
+      <c r="C41" s="6">
+        <v>4</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>35</v>
+      </c>
+      <c r="B42">
+        <v>8</v>
+      </c>
+      <c r="C42" s="1">
+        <v>4</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>36</v>
+      </c>
+      <c r="B43">
+        <v>8</v>
+      </c>
+      <c r="C43" s="6">
+        <v>4</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>37</v>
+      </c>
+      <c r="B44">
+        <v>9</v>
+      </c>
+      <c r="C44" s="1">
+        <v>3</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>38</v>
+      </c>
+      <c r="B45">
+        <v>9</v>
+      </c>
+      <c r="C45" s="6">
+        <v>3</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>39</v>
+      </c>
+      <c r="B46">
+        <v>9</v>
+      </c>
+      <c r="C46" s="1">
+        <v>4</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>40</v>
+      </c>
+      <c r="B47">
+        <v>9</v>
+      </c>
+      <c r="C47" s="6">
+        <v>4</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D48" s="6"/>
+    </row>
+    <row r="49" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D49" s="6"/>
+    </row>
+    <row r="50" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D50" s="6"/>
+    </row>
+    <row r="51" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D51" s="6"/>
+    </row>
+    <row r="52" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D52" s="6"/>
+    </row>
+    <row r="53" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D53" s="6"/>
+    </row>
+    <row r="54" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D54" s="6"/>
+    </row>
+    <row r="55" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D55" s="6"/>
+    </row>
+    <row r="56" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D56" s="6"/>
+    </row>
+    <row r="57" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D57" s="6"/>
+    </row>
+    <row r="58" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D58" s="6"/>
+    </row>
+    <row r="59" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D59" s="6"/>
+    </row>
+    <row r="60" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D60" s="6"/>
+    </row>
+    <row r="61" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D61" s="6"/>
+    </row>
+    <row r="62" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D62" s="6"/>
+    </row>
+    <row r="63" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D63" s="6"/>
+    </row>
+    <row r="64" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D64" s="6"/>
+    </row>
+    <row r="65" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D65" s="6"/>
+    </row>
+    <row r="66" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D66" s="6"/>
+    </row>
+    <row r="67" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D67" s="6"/>
+    </row>
+    <row r="68" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D68" s="6"/>
+    </row>
+    <row r="118" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D118" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD7FB523-CD2C-4A07-B6B4-D1544975ADF1}">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.5546875" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.44140625" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" ht="16.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>2</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>4</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>5</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>6</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>8</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/doc/docs/股票配置.xlsx
+++ b/doc/docs/股票配置.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\proj\unityProj\Line\doc\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E66D6846-FD9A-48DA-826B-1CC1F5DA8F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3BC8EB-6E7E-4975-A5AB-C5EA3A3C3E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="504" windowWidth="30984" windowHeight="16560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="12240" windowWidth="22149" windowHeight="11829" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="股票属性" sheetId="6" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="202">
   <si>
     <t>Horizontal</t>
   </si>
@@ -87,38 +87,14 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>["2","8#2*2"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>["5"]</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>["5","8#2*2"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>冒险与突破</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>["20#3","3*2","10#1"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["20#1","21#1*1","3*1","19*2"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["20#2","14#1","3"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["20#3","14#2","13#2*2","2#4","3*4"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>desc#string</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -169,22 +145,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>["20#3","21*2","6#1"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["20#1","21#1*1","6#1"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["20#2","14#1","6"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["20#3","10#2","13#2*2","5#4","6*4"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>emotion#int</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -193,14 +153,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>["5","9#2","21*1"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["9","8*1","13#1*1"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>["15","21"]</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -209,10 +161,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>["19#2","8","5#1","2#1*1"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>["14","2"]</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -225,94 +173,18 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>["5#2","18#2*1","16@2"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["5#4","16*2","9*4"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["2","17#6","9*4"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["5","18#4","16*2"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["2#4","16*2","12*4"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["20#4","21*4","8","19#2*3"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["6#1","4#2*1","12*1"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["20#2","4#2*1","7*3","21*3"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["13","16#2","9#2*1"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["4#1","10","11*1","7*2"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["17","16*1","5#2"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>["16","13*2"]</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>["17","9#2","14*2"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>["5","18","21"]</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>["5#1","2*1","19","10"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["19","8*1","13#2"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["18","14*1","3#2"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>StockAttr</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>key#string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>effect1#string[]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>effect2#string[]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>effect3#string[]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>词条id</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -368,10 +240,6 @@
     <t>每日公司业绩额外上升0.1，若业绩上升，再放大10%</t>
   </si>
   <si>
-    <t>["Add#0.1","UpScale#1.1"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>高歌</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -383,10 +251,6 @@
     <t>每日公司业绩额外上升0.3，若业绩上升，再放大20%</t>
   </si>
   <si>
-    <t>["Add#0.3","UpScale1.2"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>火箭</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -398,10 +262,6 @@
     <t>每日公司业绩额外上升0.5，若业绩上升，再放大30%</t>
   </si>
   <si>
-    <t>["Add#0.5","UpScale#1.3"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>滑坡</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -413,10 +273,6 @@
     <t>每日公司业绩额外下降0.1，若业绩下降，再放大10%</t>
   </si>
   <si>
-    <t>["Add#-0.1","DownScale#1.1"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>摔落</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -428,10 +284,6 @@
     <t>每日公司业绩额外下降0.3，若业绩下降，再放大20%</t>
   </si>
   <si>
-    <t>["Add#-0.3","DownScale#1.1"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>断崖</t>
   </si>
   <si>
@@ -442,10 +294,6 @@
     <t>每日公司业绩额外下降0.5，若业绩下降，再放大30%</t>
   </si>
   <si>
-    <t>["Add#-0.5","DownScale#1.3"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>摇摆</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -457,10 +305,6 @@
     <t>每日，若上个交易日公司业绩上升，则此次业绩缩减15%，若上个交易日公司业绩下降，则此次业绩放大15%</t>
   </si>
   <si>
-    <t>["UpScaleLast#0.85","DownScaleLast#1.15"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>懒散</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -472,10 +316,6 @@
     <t>每日，公司业绩变化缩减30%</t>
   </si>
   <si>
-    <t>["Scale#0.3"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>敏感</t>
   </si>
   <si>
@@ -486,10 +326,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>["Transfer#1#2#0.08"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>盲从</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -502,10 +338,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>["Transfer#1#3#0.08"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>腐败</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -518,14 +350,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>["Transfer#1#2#0.05*1","Transfer#1#3#0.05*1"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["GrowAdd#1#0.05","AttrAdd#5#-1"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>混乱</t>
   </si>
   <si>
@@ -536,10 +360,6 @@
     <t>每日，1/3概率业绩上升0.4，1/3概率业绩放大30%，1/3概率业绩下降0.6</t>
   </si>
   <si>
-    <t>["Add#0.4%1","Scale#1.3%1","Add#-0.6%1"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>创新</t>
   </si>
   <si>
@@ -550,10 +370,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>["Transfer#3#1#0.08"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>衰老</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -566,14 +382,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>["Add#-0.15*1"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["GrowAdd#1#0.2"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>生长</t>
   </si>
   <si>
@@ -585,18 +393,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>["Transfer#3#1#0.08%0.33"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["Add#0.2*1"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["GrowAdd#1#0.1"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>扩张</t>
   </si>
   <si>
@@ -608,18 +404,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>["Transfer#1#2#0.2*1"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["Scale#1.35*2"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["GrowAdd#1#-0.08","GrowAdd#2#-0.07"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>精简</t>
   </si>
   <si>
@@ -630,18 +414,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>["Transfer#3#1#0.1*1"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["Scale#0.8*2"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["GrowAdd#1#0.08","GrowAdd#2#0.05"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>整顿</t>
   </si>
   <si>
@@ -652,14 +424,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>["Transfer#2#1#0.05*1","Transfer#3#1#0.05*1"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["GrowAdd#1#0.03","AttrPurify#1%0.3"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>冒险</t>
   </si>
   <si>
@@ -671,10 +435,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>["Transfer#3#2#0.08"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>停滞</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -683,10 +443,6 @@
   </si>
   <si>
     <t>每回合8%市场敏感度变为行业冲击乘数</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["Transfer#2#3#0.08"]</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -795,6 +551,205 @@
   <si>
     <t>enum#StockAttrType</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Add/0.1","UpScale/1.1"]</t>
+  </si>
+  <si>
+    <t>["Add/0.3","UpScale1.2"]</t>
+  </si>
+  <si>
+    <t>["Add/0.5","UpScale/1.3"]</t>
+  </si>
+  <si>
+    <t>["Add/-0.1","DownScale/1.1"]</t>
+  </si>
+  <si>
+    <t>["Add/-0.3","DownScale/1.1"]</t>
+  </si>
+  <si>
+    <t>["Add/-0.5","DownScale/1.3"]</t>
+  </si>
+  <si>
+    <t>["UpScaleLast/0.85","DownScaleLast/1.15"]</t>
+  </si>
+  <si>
+    <t>["Scale/0.3"]</t>
+  </si>
+  <si>
+    <t>["Transfer/1/2/0.08"]</t>
+  </si>
+  <si>
+    <t>["Transfer/1/3/0.08"]</t>
+  </si>
+  <si>
+    <t>["Transfer/1/2/0.05*1","Transfer/1/3/0.05*1"]</t>
+  </si>
+  <si>
+    <t>["GrowAdd/1/0.05","AttrAdd/5/-1"]</t>
+  </si>
+  <si>
+    <t>["Add/0.4%1","Scale/1.3%1","Add/-0.6%1"]</t>
+  </si>
+  <si>
+    <t>["Transfer/3/1/0.08"]</t>
+  </si>
+  <si>
+    <t>["Add/-0.15*1"]</t>
+  </si>
+  <si>
+    <t>["GrowAdd/1/0.2"]</t>
+  </si>
+  <si>
+    <t>["Transfer/3/1/0.08%0.33"]</t>
+  </si>
+  <si>
+    <t>["Add/0.2*1"]</t>
+  </si>
+  <si>
+    <t>["GrowAdd/1/0.1"]</t>
+  </si>
+  <si>
+    <t>["Transfer/1/2/0.2*1"]</t>
+  </si>
+  <si>
+    <t>["Scale/1.35*2"]</t>
+  </si>
+  <si>
+    <t>["GrowAdd/1/-0.08","GrowAdd/2/-0.07"]</t>
+  </si>
+  <si>
+    <t>["Transfer/3/1/0.1*1"]</t>
+  </si>
+  <si>
+    <t>["Scale/0.8*2"]</t>
+  </si>
+  <si>
+    <t>["GrowAdd/1/0.08","GrowAdd/2/0.05"]</t>
+  </si>
+  <si>
+    <t>["Transfer/2/1/0.05*1","Transfer/3/1/0.05*1"]</t>
+  </si>
+  <si>
+    <t>["GrowAdd/1/0.03","AttrPurify/1%0.3"]</t>
+  </si>
+  <si>
+    <t>["Transfer/3/2/0.08"]</t>
+  </si>
+  <si>
+    <t>["Transfer/2/3/0.08"]</t>
+  </si>
+  <si>
+    <t>effect1#string[]</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect2#string[]</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect3#string[]</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>id#int</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>name#string</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>key#string</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>desc#string</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>["2","8/2*2"]</t>
+  </si>
+  <si>
+    <t>["5","8/2*2"]</t>
+  </si>
+  <si>
+    <t>["20/3","3*2","10/1"]</t>
+  </si>
+  <si>
+    <t>["20/1","21/1*1","3*1","19*2"]</t>
+  </si>
+  <si>
+    <t>["20/2","14/1","3"]</t>
+  </si>
+  <si>
+    <t>["20/3","14/2","13/2*2","2/4","3*4"]</t>
+  </si>
+  <si>
+    <t>["20/3","21*2","6/1"]</t>
+  </si>
+  <si>
+    <t>["20/1","21/1*1","6/1"]</t>
+  </si>
+  <si>
+    <t>["20/2","14/1","6"]</t>
+  </si>
+  <si>
+    <t>["20/3","10/2","13/2*2","5/4","6*4"]</t>
+  </si>
+  <si>
+    <t>["5","9/2","21*1"]</t>
+  </si>
+  <si>
+    <t>["9","8*1","13/1*1"]</t>
+  </si>
+  <si>
+    <t>["19/2","8","5/1","2/1*1"]</t>
+  </si>
+  <si>
+    <t>["5/2","18/2*1","16@2"]</t>
+  </si>
+  <si>
+    <t>["5/4","16*2","9*4"]</t>
+  </si>
+  <si>
+    <t>["2","17/6","9*4"]</t>
+  </si>
+  <si>
+    <t>["5","18/4","16*2"]</t>
+  </si>
+  <si>
+    <t>["2/4","16*2","12*4"]</t>
+  </si>
+  <si>
+    <t>["20/4","21*4","8","19/2*3"]</t>
+  </si>
+  <si>
+    <t>["6/1","4/2*1","12*1"]</t>
+  </si>
+  <si>
+    <t>["20/2","4/2*1","7*3","21*3"]</t>
+  </si>
+  <si>
+    <t>["13","16/2","9/2*1"]</t>
+  </si>
+  <si>
+    <t>["4/1","10","11*1","7*2"]</t>
+  </si>
+  <si>
+    <t>["17","16*1","5/2"]</t>
+  </si>
+  <si>
+    <t>["17","9/2","14*2"]</t>
+  </si>
+  <si>
+    <t>["5/1","2*1","19","10"]</t>
+  </si>
+  <si>
+    <t>["19","8*1","13/2"]</t>
+  </si>
+  <si>
+    <t>["18","14*1","3/2"]</t>
   </si>
 </sst>
 </file>
@@ -1224,7 +1179,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1235,25 +1190,25 @@
     </row>
     <row r="2" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>171</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>67</v>
+        <v>172</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>68</v>
+        <v>167</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>69</v>
+        <v>168</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -1263,7 +1218,7 @@
     </row>
     <row r="3" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>198</v>
+        <v>137</v>
       </c>
       <c r="B3" s="1"/>
       <c r="D3" s="1"/>
@@ -1317,25 +1272,25 @@
     </row>
     <row r="7" spans="1:12" ht="16.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -1347,22 +1302,22 @@
         <v>1</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
@@ -1372,22 +1327,22 @@
         <v>2</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>85</v>
+        <v>138</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
@@ -1397,22 +1352,22 @@
         <v>3</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>89</v>
+        <v>139</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
@@ -1422,22 +1377,22 @@
         <v>4</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>93</v>
+        <v>140</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
@@ -1445,22 +1400,22 @@
         <v>5</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
@@ -1468,22 +1423,22 @@
         <v>6</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
@@ -1491,22 +1446,22 @@
         <v>7</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
@@ -1514,22 +1469,22 @@
         <v>8</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
@@ -1537,22 +1492,22 @@
         <v>9</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
@@ -1560,22 +1515,22 @@
         <v>10</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
@@ -1583,22 +1538,22 @@
         <v>11</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
@@ -1606,22 +1561,22 @@
         <v>12</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>123</v>
+        <v>81</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
@@ -1629,22 +1584,22 @@
         <v>13</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>129</v>
+        <v>85</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
@@ -1652,22 +1607,22 @@
         <v>14</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>131</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
@@ -1675,22 +1630,22 @@
         <v>15</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>137</v>
+        <v>91</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
@@ -1698,22 +1653,22 @@
         <v>16</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
@@ -1721,22 +1676,22 @@
         <v>17</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>146</v>
+        <v>95</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>147</v>
+        <v>96</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
@@ -1744,22 +1699,22 @@
         <v>18</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>152</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>153</v>
+        <v>99</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>154</v>
+        <v>100</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
@@ -1767,22 +1722,22 @@
         <v>19</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>158</v>
+        <v>101</v>
       </c>
       <c r="C26" t="s">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>160</v>
+        <v>103</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
@@ -1790,22 +1745,22 @@
         <v>20</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>164</v>
+        <v>105</v>
       </c>
       <c r="D27" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="F27" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="16.2" x14ac:dyDescent="0.25">
@@ -1813,22 +1768,22 @@
         <v>21</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>167</v>
+        <v>107</v>
       </c>
       <c r="C28" t="s">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1847,255 +1802,255 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>197</v>
+        <v>136</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>171</v>
+        <v>110</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>172</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>173</v>
+        <v>112</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>174</v>
+        <v>113</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>175</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>176</v>
+        <v>115</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>177</v>
+        <v>116</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>178</v>
+        <v>117</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>179</v>
+        <v>118</v>
       </c>
       <c r="B6">
         <v>4</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>180</v>
+        <v>119</v>
       </c>
       <c r="B7" s="1">
         <v>5</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>181</v>
+        <v>120</v>
       </c>
       <c r="B8" s="1">
         <v>6</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>182</v>
+        <v>121</v>
       </c>
       <c r="B9" s="1">
         <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>183</v>
+        <v>122</v>
       </c>
       <c r="B10" s="1">
         <v>8</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>184</v>
+        <v>123</v>
       </c>
       <c r="B11" s="1">
         <v>9</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>185</v>
+        <v>124</v>
       </c>
       <c r="B12" s="1">
         <v>10</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>186</v>
+        <v>125</v>
       </c>
       <c r="B13" s="1">
         <v>11</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>187</v>
+        <v>126</v>
       </c>
       <c r="B14" s="1">
         <v>12</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>188</v>
+        <v>127</v>
       </c>
       <c r="B15" s="1">
         <v>13</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>189</v>
+        <v>128</v>
       </c>
       <c r="B16" s="1">
         <v>14</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>131</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>190</v>
+        <v>129</v>
       </c>
       <c r="B17" s="1">
         <v>15</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>191</v>
+        <v>130</v>
       </c>
       <c r="B18" s="1">
         <v>16</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>140</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>192</v>
+        <v>131</v>
       </c>
       <c r="B19" s="1">
         <v>17</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>146</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="B20" s="1">
         <v>18</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>152</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>194</v>
+        <v>133</v>
       </c>
       <c r="B21" s="1">
         <v>19</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>158</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>195</v>
+        <v>134</v>
       </c>
       <c r="B22" s="1">
         <v>20</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>163</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>196</v>
+        <v>135</v>
       </c>
       <c r="B23" s="1">
         <v>21</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>167</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -2125,7 +2080,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2236,7 +2191,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>13</v>
+        <v>174</v>
       </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
@@ -2282,7 +2237,7 @@
         <v>3</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
@@ -2296,7 +2251,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>15</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
@@ -2310,7 +2265,7 @@
         <v>2</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
@@ -2324,7 +2279,7 @@
         <v>4</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>17</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
@@ -2338,7 +2293,7 @@
         <v>3</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>18</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2352,7 +2307,7 @@
         <v>2</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>19</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2366,7 +2321,7 @@
         <v>5</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>20</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2380,7 +2335,7 @@
         <v>4</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>35</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2394,7 +2349,7 @@
         <v>3</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>36</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2408,7 +2363,7 @@
         <v>2</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>37</v>
+        <v>182</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2422,7 +2377,7 @@
         <v>5</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>38</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2436,7 +2391,7 @@
         <v>3</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>41</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2450,7 +2405,7 @@
         <v>3</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>42</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2464,7 +2419,7 @@
         <v>2</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2478,7 +2433,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2492,7 +2447,7 @@
         <v>3</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>45</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2506,7 +2461,7 @@
         <v>3</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2520,7 +2475,7 @@
         <v>2</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2534,7 +2489,7 @@
         <v>1</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2548,7 +2503,7 @@
         <v>5</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>49</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2562,7 +2517,7 @@
         <v>7</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>50</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2576,7 +2531,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>51</v>
+        <v>189</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2590,7 +2545,7 @@
         <v>6</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2604,7 +2559,7 @@
         <v>7</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2618,7 +2573,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>54</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2632,7 +2587,7 @@
         <v>5</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>55</v>
+        <v>193</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2646,7 +2601,7 @@
         <v>5</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>56</v>
+        <v>194</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2660,7 +2615,7 @@
         <v>4</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>57</v>
+        <v>195</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2674,7 +2629,7 @@
         <v>3</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>58</v>
+        <v>196</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2688,7 +2643,7 @@
         <v>4</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>59</v>
+        <v>197</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2702,7 +2657,7 @@
         <v>4</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2716,7 +2671,7 @@
         <v>4</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>61</v>
+        <v>198</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2730,7 +2685,7 @@
         <v>3</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2744,7 +2699,7 @@
         <v>3</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>63</v>
+        <v>199</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2758,7 +2713,7 @@
         <v>4</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>64</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2772,7 +2727,7 @@
         <v>4</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>65</v>
+        <v>201</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2860,7 +2815,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2876,10 +2831,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.2" x14ac:dyDescent="0.25">
@@ -2918,10 +2873,10 @@
         <v>8</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.25">
@@ -2932,7 +2887,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -2943,10 +2898,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -2957,10 +2912,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -2971,7 +2926,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -2982,7 +2937,7 @@
         <v>5</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2993,7 +2948,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -3004,7 +2959,7 @@
         <v>7</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -3015,7 +2970,7 @@
         <v>8</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -3026,7 +2981,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>1</v>
